--- a/can2tsn_history.xlsx
+++ b/can2tsn_history.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="355">
   <si>
     <t>TimeStamp</t>
   </si>
@@ -991,6 +991,96 @@
   <si>
     <t>2025-05-09 03:43:57</t>
   </si>
+  <si>
+    <t>2025-05-09 13:32:02</t>
+  </si>
+  <si>
+    <t>2025-05-09 13:36:38</t>
+  </si>
+  <si>
+    <t>2025-05-09 13:38:29</t>
+  </si>
+  <si>
+    <t>2025-05-09 13:38:48</t>
+  </si>
+  <si>
+    <t>2025-05-09 13:47:53</t>
+  </si>
+  <si>
+    <t>2025-05-09 13:48:33</t>
+  </si>
+  <si>
+    <t>2025-05-09 13:54:58</t>
+  </si>
+  <si>
+    <t>2025-05-09 13:58:23</t>
+  </si>
+  <si>
+    <t>2025-05-09 14:00:04</t>
+  </si>
+  <si>
+    <t>2025-05-09 14:00:25</t>
+  </si>
+  <si>
+    <t>2025-05-09 14:02:02</t>
+  </si>
+  <si>
+    <t>2025-05-09 14:03:18</t>
+  </si>
+  <si>
+    <t>2025-05-09 14:05:54</t>
+  </si>
+  <si>
+    <t>2025-05-09 14:35:03</t>
+  </si>
+  <si>
+    <t>2025-05-09 14:38:00</t>
+  </si>
+  <si>
+    <t>2025-05-09 16:01:42</t>
+  </si>
+  <si>
+    <t>2025-05-09 16:01:51</t>
+  </si>
+  <si>
+    <t>2025-05-09 16:11:50</t>
+  </si>
+  <si>
+    <t>2025-05-09 16:19:38</t>
+  </si>
+  <si>
+    <t>2025-05-09 16:23:59</t>
+  </si>
+  <si>
+    <t>2025-05-09 16:27:43</t>
+  </si>
+  <si>
+    <t>2025-05-09 16:28:05</t>
+  </si>
+  <si>
+    <t>2025-05-09 16:28:35</t>
+  </si>
+  <si>
+    <t>2025-05-09 16:29:05</t>
+  </si>
+  <si>
+    <t>2025-05-09 16:30:02</t>
+  </si>
+  <si>
+    <t>2025-05-09 16:40:00</t>
+  </si>
+  <si>
+    <t>2025-05-09 16:47:55</t>
+  </si>
+  <si>
+    <t>2025-05-09 16:48:31</t>
+  </si>
+  <si>
+    <t>2025-05-09 17:40:28</t>
+  </si>
+  <si>
+    <t>2025-05-09 17:47:56</t>
+  </si>
 </sst>
 </file>
 
@@ -69682,6 +69772,2766 @@
         <v>27.209112</v>
       </c>
     </row>
+    <row r="2974">
+      <c r="A2974" t="s">
+        <v>325</v>
+      </c>
+      <c r="B2974" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2974">
+        <v>20</v>
+      </c>
+      <c r="D2974">
+        <v>353300</v>
+      </c>
+      <c r="E2974">
+        <v>3533</v>
+      </c>
+      <c r="F2974">
+        <v>0</v>
+      </c>
+      <c r="G2974">
+        <v>18.303365</v>
+      </c>
+    </row>
+    <row r="2975">
+      <c r="A2975" t="s">
+        <v>325</v>
+      </c>
+      <c r="B2975" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2975">
+        <v>20</v>
+      </c>
+      <c r="D2975">
+        <v>353300</v>
+      </c>
+      <c r="E2975">
+        <v>3533</v>
+      </c>
+      <c r="F2975">
+        <v>0</v>
+      </c>
+      <c r="G2975">
+        <v>19.328279000000002</v>
+      </c>
+    </row>
+    <row r="2976">
+      <c r="A2976" t="s">
+        <v>325</v>
+      </c>
+      <c r="B2976" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2976">
+        <v>20</v>
+      </c>
+      <c r="D2976">
+        <v>3923600</v>
+      </c>
+      <c r="E2976">
+        <v>39236</v>
+      </c>
+      <c r="F2976">
+        <v>0</v>
+      </c>
+      <c r="G2976">
+        <v>10.802338</v>
+      </c>
+    </row>
+    <row r="2977">
+      <c r="A2977" t="s">
+        <v>325</v>
+      </c>
+      <c r="B2977" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2977">
+        <v>20</v>
+      </c>
+      <c r="D2977">
+        <v>362700</v>
+      </c>
+      <c r="E2977">
+        <v>3627</v>
+      </c>
+      <c r="F2977">
+        <v>0</v>
+      </c>
+      <c r="G2977">
+        <v>18.007354</v>
+      </c>
+    </row>
+    <row r="2978">
+      <c r="A2978" t="s">
+        <v>326</v>
+      </c>
+      <c r="B2978" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2978">
+        <v>20</v>
+      </c>
+      <c r="D2978">
+        <v>352500</v>
+      </c>
+      <c r="E2978">
+        <v>3525</v>
+      </c>
+      <c r="F2978">
+        <v>0</v>
+      </c>
+      <c r="G2978">
+        <v>19.806493</v>
+      </c>
+    </row>
+    <row r="2979">
+      <c r="A2979" t="s">
+        <v>326</v>
+      </c>
+      <c r="B2979" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2979">
+        <v>20</v>
+      </c>
+      <c r="D2979">
+        <v>352500</v>
+      </c>
+      <c r="E2979">
+        <v>3525</v>
+      </c>
+      <c r="F2979">
+        <v>0</v>
+      </c>
+      <c r="G2979">
+        <v>16.06241</v>
+      </c>
+    </row>
+    <row r="2980">
+      <c r="A2980" t="s">
+        <v>326</v>
+      </c>
+      <c r="B2980" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2980">
+        <v>20</v>
+      </c>
+      <c r="D2980">
+        <v>3908000</v>
+      </c>
+      <c r="E2980">
+        <v>39080</v>
+      </c>
+      <c r="F2980">
+        <v>0</v>
+      </c>
+      <c r="G2980">
+        <v>9.889334</v>
+      </c>
+    </row>
+    <row r="2981">
+      <c r="A2981" t="s">
+        <v>326</v>
+      </c>
+      <c r="B2981" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2981">
+        <v>20</v>
+      </c>
+      <c r="D2981">
+        <v>354000</v>
+      </c>
+      <c r="E2981">
+        <v>3540</v>
+      </c>
+      <c r="F2981">
+        <v>0</v>
+      </c>
+      <c r="G2981">
+        <v>20.324740000000002</v>
+      </c>
+    </row>
+    <row r="2982">
+      <c r="A2982" t="s">
+        <v>327</v>
+      </c>
+      <c r="B2982" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2982">
+        <v>20</v>
+      </c>
+      <c r="D2982">
+        <v>347400</v>
+      </c>
+      <c r="E2982">
+        <v>3474</v>
+      </c>
+      <c r="F2982">
+        <v>0</v>
+      </c>
+      <c r="G2982">
+        <v>18.912095</v>
+      </c>
+    </row>
+    <row r="2983">
+      <c r="A2983" t="s">
+        <v>327</v>
+      </c>
+      <c r="B2983" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2983">
+        <v>20</v>
+      </c>
+      <c r="D2983">
+        <v>347400</v>
+      </c>
+      <c r="E2983">
+        <v>3474</v>
+      </c>
+      <c r="F2983">
+        <v>0</v>
+      </c>
+      <c r="G2983">
+        <v>16.201507</v>
+      </c>
+    </row>
+    <row r="2984">
+      <c r="A2984" t="s">
+        <v>327</v>
+      </c>
+      <c r="B2984" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2984">
+        <v>20</v>
+      </c>
+      <c r="D2984">
+        <v>3915500</v>
+      </c>
+      <c r="E2984">
+        <v>39155</v>
+      </c>
+      <c r="F2984">
+        <v>0</v>
+      </c>
+      <c r="G2984">
+        <v>11.468924</v>
+      </c>
+    </row>
+    <row r="2985">
+      <c r="A2985" t="s">
+        <v>327</v>
+      </c>
+      <c r="B2985" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2985">
+        <v>20</v>
+      </c>
+      <c r="D2985">
+        <v>358400</v>
+      </c>
+      <c r="E2985">
+        <v>3584</v>
+      </c>
+      <c r="F2985">
+        <v>0</v>
+      </c>
+      <c r="G2985">
+        <v>17.858465</v>
+      </c>
+    </row>
+    <row r="2986">
+      <c r="A2986" t="s">
+        <v>328</v>
+      </c>
+      <c r="B2986" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2986">
+        <v>20</v>
+      </c>
+      <c r="D2986">
+        <v>341400</v>
+      </c>
+      <c r="E2986">
+        <v>3414</v>
+      </c>
+      <c r="F2986">
+        <v>0</v>
+      </c>
+      <c r="G2986">
+        <v>18.602959</v>
+      </c>
+    </row>
+    <row r="2987">
+      <c r="A2987" t="s">
+        <v>328</v>
+      </c>
+      <c r="B2987" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2987">
+        <v>20</v>
+      </c>
+      <c r="D2987">
+        <v>341400</v>
+      </c>
+      <c r="E2987">
+        <v>3414</v>
+      </c>
+      <c r="F2987">
+        <v>0</v>
+      </c>
+      <c r="G2987">
+        <v>16.585491</v>
+      </c>
+    </row>
+    <row r="2988">
+      <c r="A2988" t="s">
+        <v>328</v>
+      </c>
+      <c r="B2988" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2988">
+        <v>20</v>
+      </c>
+      <c r="D2988">
+        <v>3907900</v>
+      </c>
+      <c r="E2988">
+        <v>39079</v>
+      </c>
+      <c r="F2988">
+        <v>0</v>
+      </c>
+      <c r="G2988">
+        <v>9.593504</v>
+      </c>
+    </row>
+    <row r="2989">
+      <c r="A2989" t="s">
+        <v>328</v>
+      </c>
+      <c r="B2989" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2989">
+        <v>20</v>
+      </c>
+      <c r="D2989">
+        <v>364600</v>
+      </c>
+      <c r="E2989">
+        <v>3646</v>
+      </c>
+      <c r="F2989">
+        <v>0</v>
+      </c>
+      <c r="G2989">
+        <v>21.707003</v>
+      </c>
+    </row>
+    <row r="2990">
+      <c r="A2990" t="s">
+        <v>329</v>
+      </c>
+      <c r="B2990" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2990">
+        <v>20</v>
+      </c>
+      <c r="D2990">
+        <v>335200</v>
+      </c>
+      <c r="E2990">
+        <v>3352</v>
+      </c>
+      <c r="F2990">
+        <v>0</v>
+      </c>
+      <c r="G2990">
+        <v>17.982646000000003</v>
+      </c>
+    </row>
+    <row r="2991">
+      <c r="A2991" t="s">
+        <v>329</v>
+      </c>
+      <c r="B2991" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2991">
+        <v>20</v>
+      </c>
+      <c r="D2991">
+        <v>335200</v>
+      </c>
+      <c r="E2991">
+        <v>3352</v>
+      </c>
+      <c r="F2991">
+        <v>0</v>
+      </c>
+      <c r="G2991">
+        <v>17.819288</v>
+      </c>
+    </row>
+    <row r="2992">
+      <c r="A2992" t="s">
+        <v>329</v>
+      </c>
+      <c r="B2992" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2992">
+        <v>20</v>
+      </c>
+      <c r="D2992">
+        <v>3898100</v>
+      </c>
+      <c r="E2992">
+        <v>38981</v>
+      </c>
+      <c r="F2992">
+        <v>0</v>
+      </c>
+      <c r="G2992">
+        <v>10.129235</v>
+      </c>
+    </row>
+    <row r="2993">
+      <c r="A2993" t="s">
+        <v>329</v>
+      </c>
+      <c r="B2993" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2993">
+        <v>20</v>
+      </c>
+      <c r="D2993">
+        <v>372400</v>
+      </c>
+      <c r="E2993">
+        <v>3724</v>
+      </c>
+      <c r="F2993">
+        <v>0</v>
+      </c>
+      <c r="G2993">
+        <v>18.151422</v>
+      </c>
+    </row>
+    <row r="2994">
+      <c r="A2994" t="s">
+        <v>330</v>
+      </c>
+      <c r="B2994" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2994">
+        <v>20</v>
+      </c>
+      <c r="D2994">
+        <v>357400</v>
+      </c>
+      <c r="E2994">
+        <v>3574</v>
+      </c>
+      <c r="F2994">
+        <v>0</v>
+      </c>
+      <c r="G2994">
+        <v>16.965835</v>
+      </c>
+    </row>
+    <row r="2995">
+      <c r="A2995" t="s">
+        <v>330</v>
+      </c>
+      <c r="B2995" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2995">
+        <v>20</v>
+      </c>
+      <c r="D2995">
+        <v>357400</v>
+      </c>
+      <c r="E2995">
+        <v>3574</v>
+      </c>
+      <c r="F2995">
+        <v>0</v>
+      </c>
+      <c r="G2995">
+        <v>15.885526</v>
+      </c>
+    </row>
+    <row r="2996">
+      <c r="A2996" t="s">
+        <v>330</v>
+      </c>
+      <c r="B2996" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2996">
+        <v>20</v>
+      </c>
+      <c r="D2996">
+        <v>3904300</v>
+      </c>
+      <c r="E2996">
+        <v>39043</v>
+      </c>
+      <c r="F2996">
+        <v>0</v>
+      </c>
+      <c r="G2996">
+        <v>9.545201</v>
+      </c>
+    </row>
+    <row r="2997">
+      <c r="A2997" t="s">
+        <v>330</v>
+      </c>
+      <c r="B2997" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2997">
+        <v>20</v>
+      </c>
+      <c r="D2997">
+        <v>360400</v>
+      </c>
+      <c r="E2997">
+        <v>3604</v>
+      </c>
+      <c r="F2997">
+        <v>0</v>
+      </c>
+      <c r="G2997">
+        <v>18.615993</v>
+      </c>
+    </row>
+    <row r="2998">
+      <c r="A2998" t="s">
+        <v>331</v>
+      </c>
+      <c r="B2998" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2998">
+        <v>20</v>
+      </c>
+      <c r="D2998">
+        <v>346700</v>
+      </c>
+      <c r="E2998">
+        <v>3467</v>
+      </c>
+      <c r="F2998">
+        <v>0</v>
+      </c>
+      <c r="G2998">
+        <v>20.12769</v>
+      </c>
+    </row>
+    <row r="2999">
+      <c r="A2999" t="s">
+        <v>331</v>
+      </c>
+      <c r="B2999" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2999">
+        <v>20</v>
+      </c>
+      <c r="D2999">
+        <v>346700</v>
+      </c>
+      <c r="E2999">
+        <v>3467</v>
+      </c>
+      <c r="F2999">
+        <v>0</v>
+      </c>
+      <c r="G2999">
+        <v>22.614727000000002</v>
+      </c>
+    </row>
+    <row r="3000">
+      <c r="A3000" t="s">
+        <v>331</v>
+      </c>
+      <c r="B3000" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3000">
+        <v>20</v>
+      </c>
+      <c r="D3000">
+        <v>3909300</v>
+      </c>
+      <c r="E3000">
+        <v>39093</v>
+      </c>
+      <c r="F3000">
+        <v>0</v>
+      </c>
+      <c r="G3000">
+        <v>32.922203999999994</v>
+      </c>
+    </row>
+    <row r="3001">
+      <c r="A3001" t="s">
+        <v>331</v>
+      </c>
+      <c r="B3001" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3001">
+        <v>20</v>
+      </c>
+      <c r="D3001">
+        <v>365000</v>
+      </c>
+      <c r="E3001">
+        <v>3650</v>
+      </c>
+      <c r="F3001">
+        <v>0</v>
+      </c>
+      <c r="G3001">
+        <v>23.727135999999998</v>
+      </c>
+    </row>
+    <row r="3002">
+      <c r="A3002" t="s">
+        <v>332</v>
+      </c>
+      <c r="B3002" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3002">
+        <v>20</v>
+      </c>
+      <c r="D3002">
+        <v>336300</v>
+      </c>
+      <c r="E3002">
+        <v>3363</v>
+      </c>
+      <c r="F3002">
+        <v>0</v>
+      </c>
+      <c r="G3002">
+        <v>18.237084</v>
+      </c>
+    </row>
+    <row r="3003">
+      <c r="A3003" t="s">
+        <v>332</v>
+      </c>
+      <c r="B3003" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3003">
+        <v>20</v>
+      </c>
+      <c r="D3003">
+        <v>336300</v>
+      </c>
+      <c r="E3003">
+        <v>3363</v>
+      </c>
+      <c r="F3003">
+        <v>0</v>
+      </c>
+      <c r="G3003">
+        <v>19.084595</v>
+      </c>
+    </row>
+    <row r="3004">
+      <c r="A3004" t="s">
+        <v>332</v>
+      </c>
+      <c r="B3004" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3004">
+        <v>20</v>
+      </c>
+      <c r="D3004">
+        <v>3914300</v>
+      </c>
+      <c r="E3004">
+        <v>39143</v>
+      </c>
+      <c r="F3004">
+        <v>0</v>
+      </c>
+      <c r="G3004">
+        <v>9.616214999999999</v>
+      </c>
+    </row>
+    <row r="3005">
+      <c r="A3005" t="s">
+        <v>332</v>
+      </c>
+      <c r="B3005" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3005">
+        <v>20</v>
+      </c>
+      <c r="D3005">
+        <v>375900</v>
+      </c>
+      <c r="E3005">
+        <v>3759</v>
+      </c>
+      <c r="F3005">
+        <v>0</v>
+      </c>
+      <c r="G3005">
+        <v>33.869283</v>
+      </c>
+    </row>
+    <row r="3006">
+      <c r="A3006" t="s">
+        <v>333</v>
+      </c>
+      <c r="B3006" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3006">
+        <v>20</v>
+      </c>
+      <c r="D3006">
+        <v>358100</v>
+      </c>
+      <c r="E3006">
+        <v>3581</v>
+      </c>
+      <c r="F3006">
+        <v>0</v>
+      </c>
+      <c r="G3006">
+        <v>17.341885</v>
+      </c>
+    </row>
+    <row r="3007">
+      <c r="A3007" t="s">
+        <v>333</v>
+      </c>
+      <c r="B3007" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3007">
+        <v>20</v>
+      </c>
+      <c r="D3007">
+        <v>358100</v>
+      </c>
+      <c r="E3007">
+        <v>3581</v>
+      </c>
+      <c r="F3007">
+        <v>0</v>
+      </c>
+      <c r="G3007">
+        <v>16.101311</v>
+      </c>
+    </row>
+    <row r="3008">
+      <c r="A3008" t="s">
+        <v>333</v>
+      </c>
+      <c r="B3008" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3008">
+        <v>20</v>
+      </c>
+      <c r="D3008">
+        <v>3917300</v>
+      </c>
+      <c r="E3008">
+        <v>39173</v>
+      </c>
+      <c r="F3008">
+        <v>0</v>
+      </c>
+      <c r="G3008">
+        <v>12.075868</v>
+      </c>
+    </row>
+    <row r="3009">
+      <c r="A3009" t="s">
+        <v>333</v>
+      </c>
+      <c r="B3009" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3009">
+        <v>20</v>
+      </c>
+      <c r="D3009">
+        <v>365300</v>
+      </c>
+      <c r="E3009">
+        <v>3653</v>
+      </c>
+      <c r="F3009">
+        <v>0</v>
+      </c>
+      <c r="G3009">
+        <v>29.058056</v>
+      </c>
+    </row>
+    <row r="3010">
+      <c r="A3010" t="s">
+        <v>334</v>
+      </c>
+      <c r="B3010" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3010">
+        <v>20</v>
+      </c>
+      <c r="D3010">
+        <v>352000</v>
+      </c>
+      <c r="E3010">
+        <v>3520</v>
+      </c>
+      <c r="F3010">
+        <v>0</v>
+      </c>
+      <c r="G3010">
+        <v>19.946621</v>
+      </c>
+    </row>
+    <row r="3011">
+      <c r="A3011" t="s">
+        <v>334</v>
+      </c>
+      <c r="B3011" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3011">
+        <v>20</v>
+      </c>
+      <c r="D3011">
+        <v>352000</v>
+      </c>
+      <c r="E3011">
+        <v>3520</v>
+      </c>
+      <c r="F3011">
+        <v>0</v>
+      </c>
+      <c r="G3011">
+        <v>21.874681</v>
+      </c>
+    </row>
+    <row r="3012">
+      <c r="A3012" t="s">
+        <v>334</v>
+      </c>
+      <c r="B3012" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3012">
+        <v>20</v>
+      </c>
+      <c r="D3012">
+        <v>3906700</v>
+      </c>
+      <c r="E3012">
+        <v>39067</v>
+      </c>
+      <c r="F3012">
+        <v>0</v>
+      </c>
+      <c r="G3012">
+        <v>16.735178</v>
+      </c>
+    </row>
+    <row r="3013">
+      <c r="A3013" t="s">
+        <v>334</v>
+      </c>
+      <c r="B3013" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3013">
+        <v>20</v>
+      </c>
+      <c r="D3013">
+        <v>358000</v>
+      </c>
+      <c r="E3013">
+        <v>3580</v>
+      </c>
+      <c r="F3013">
+        <v>0</v>
+      </c>
+      <c r="G3013">
+        <v>24.486214</v>
+      </c>
+    </row>
+    <row r="3014">
+      <c r="A3014" t="s">
+        <v>335</v>
+      </c>
+      <c r="B3014" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3014">
+        <v>20</v>
+      </c>
+      <c r="D3014">
+        <v>364400</v>
+      </c>
+      <c r="E3014">
+        <v>3644</v>
+      </c>
+      <c r="F3014">
+        <v>0</v>
+      </c>
+      <c r="G3014">
+        <v>17.888557</v>
+      </c>
+    </row>
+    <row r="3015">
+      <c r="A3015" t="s">
+        <v>335</v>
+      </c>
+      <c r="B3015" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3015">
+        <v>20</v>
+      </c>
+      <c r="D3015">
+        <v>364400</v>
+      </c>
+      <c r="E3015">
+        <v>3644</v>
+      </c>
+      <c r="F3015">
+        <v>0</v>
+      </c>
+      <c r="G3015">
+        <v>17.014755</v>
+      </c>
+    </row>
+    <row r="3016">
+      <c r="A3016" t="s">
+        <v>335</v>
+      </c>
+      <c r="B3016" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3016">
+        <v>20</v>
+      </c>
+      <c r="D3016">
+        <v>3923100</v>
+      </c>
+      <c r="E3016">
+        <v>39231</v>
+      </c>
+      <c r="F3016">
+        <v>0</v>
+      </c>
+      <c r="G3016">
+        <v>8.90217</v>
+      </c>
+    </row>
+    <row r="3017">
+      <c r="A3017" t="s">
+        <v>335</v>
+      </c>
+      <c r="B3017" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3017">
+        <v>20</v>
+      </c>
+      <c r="D3017">
+        <v>373000</v>
+      </c>
+      <c r="E3017">
+        <v>3730</v>
+      </c>
+      <c r="F3017">
+        <v>0</v>
+      </c>
+      <c r="G3017">
+        <v>17.830242</v>
+      </c>
+    </row>
+    <row r="3018">
+      <c r="A3018" t="s">
+        <v>336</v>
+      </c>
+      <c r="B3018" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3018">
+        <v>20</v>
+      </c>
+      <c r="D3018">
+        <v>359500</v>
+      </c>
+      <c r="E3018">
+        <v>3595</v>
+      </c>
+      <c r="F3018">
+        <v>0</v>
+      </c>
+      <c r="G3018">
+        <v>19.300248</v>
+      </c>
+    </row>
+    <row r="3019">
+      <c r="A3019" t="s">
+        <v>336</v>
+      </c>
+      <c r="B3019" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3019">
+        <v>20</v>
+      </c>
+      <c r="D3019">
+        <v>359500</v>
+      </c>
+      <c r="E3019">
+        <v>3595</v>
+      </c>
+      <c r="F3019">
+        <v>0</v>
+      </c>
+      <c r="G3019">
+        <v>16.076520000000002</v>
+      </c>
+    </row>
+    <row r="3020">
+      <c r="A3020" t="s">
+        <v>336</v>
+      </c>
+      <c r="B3020" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3020">
+        <v>20</v>
+      </c>
+      <c r="D3020">
+        <v>3922200</v>
+      </c>
+      <c r="E3020">
+        <v>39222</v>
+      </c>
+      <c r="F3020">
+        <v>0</v>
+      </c>
+      <c r="G3020">
+        <v>10.49975</v>
+      </c>
+    </row>
+    <row r="3021">
+      <c r="A3021" t="s">
+        <v>336</v>
+      </c>
+      <c r="B3021" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3021">
+        <v>20</v>
+      </c>
+      <c r="D3021">
+        <v>373700</v>
+      </c>
+      <c r="E3021">
+        <v>3737</v>
+      </c>
+      <c r="F3021">
+        <v>0</v>
+      </c>
+      <c r="G3021">
+        <v>18.206875</v>
+      </c>
+    </row>
+    <row r="3022">
+      <c r="A3022" t="s">
+        <v>337</v>
+      </c>
+      <c r="B3022" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3022">
+        <v>20</v>
+      </c>
+      <c r="D3022">
+        <v>363600</v>
+      </c>
+      <c r="E3022">
+        <v>3636</v>
+      </c>
+      <c r="F3022">
+        <v>0</v>
+      </c>
+      <c r="G3022">
+        <v>19.365766</v>
+      </c>
+    </row>
+    <row r="3023">
+      <c r="A3023" t="s">
+        <v>337</v>
+      </c>
+      <c r="B3023" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3023">
+        <v>20</v>
+      </c>
+      <c r="D3023">
+        <v>363600</v>
+      </c>
+      <c r="E3023">
+        <v>3636</v>
+      </c>
+      <c r="F3023">
+        <v>0</v>
+      </c>
+      <c r="G3023">
+        <v>18.937868</v>
+      </c>
+    </row>
+    <row r="3024">
+      <c r="A3024" t="s">
+        <v>337</v>
+      </c>
+      <c r="B3024" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3024">
+        <v>20</v>
+      </c>
+      <c r="D3024">
+        <v>3913100</v>
+      </c>
+      <c r="E3024">
+        <v>39131</v>
+      </c>
+      <c r="F3024">
+        <v>0</v>
+      </c>
+      <c r="G3024">
+        <v>12.480062</v>
+      </c>
+    </row>
+    <row r="3025">
+      <c r="A3025" t="s">
+        <v>337</v>
+      </c>
+      <c r="B3025" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3025">
+        <v>20</v>
+      </c>
+      <c r="D3025">
+        <v>369000</v>
+      </c>
+      <c r="E3025">
+        <v>3690</v>
+      </c>
+      <c r="F3025">
+        <v>0</v>
+      </c>
+      <c r="G3025">
+        <v>24.148324</v>
+      </c>
+    </row>
+    <row r="3026">
+      <c r="A3026" t="s">
+        <v>338</v>
+      </c>
+      <c r="B3026" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3026">
+        <v>20</v>
+      </c>
+      <c r="D3026">
+        <v>368600</v>
+      </c>
+      <c r="E3026">
+        <v>3686</v>
+      </c>
+      <c r="F3026">
+        <v>0</v>
+      </c>
+      <c r="G3026">
+        <v>15.952991999999998</v>
+      </c>
+    </row>
+    <row r="3027">
+      <c r="A3027" t="s">
+        <v>338</v>
+      </c>
+      <c r="B3027" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3027">
+        <v>20</v>
+      </c>
+      <c r="D3027">
+        <v>368600</v>
+      </c>
+      <c r="E3027">
+        <v>3686</v>
+      </c>
+      <c r="F3027">
+        <v>0</v>
+      </c>
+      <c r="G3027">
+        <v>20.586154999999998</v>
+      </c>
+    </row>
+    <row r="3028">
+      <c r="A3028" t="s">
+        <v>338</v>
+      </c>
+      <c r="B3028" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3028">
+        <v>20</v>
+      </c>
+      <c r="D3028">
+        <v>3905000</v>
+      </c>
+      <c r="E3028">
+        <v>39050</v>
+      </c>
+      <c r="F3028">
+        <v>0</v>
+      </c>
+      <c r="G3028">
+        <v>12.653405</v>
+      </c>
+    </row>
+    <row r="3029">
+      <c r="A3029" t="s">
+        <v>338</v>
+      </c>
+      <c r="B3029" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3029">
+        <v>20</v>
+      </c>
+      <c r="D3029">
+        <v>367400</v>
+      </c>
+      <c r="E3029">
+        <v>3674</v>
+      </c>
+      <c r="F3029">
+        <v>0</v>
+      </c>
+      <c r="G3029">
+        <v>22.755468</v>
+      </c>
+    </row>
+    <row r="3030">
+      <c r="A3030" t="s">
+        <v>339</v>
+      </c>
+      <c r="B3030" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3030">
+        <v>20</v>
+      </c>
+      <c r="D3030">
+        <v>364600</v>
+      </c>
+      <c r="E3030">
+        <v>3646</v>
+      </c>
+      <c r="F3030">
+        <v>0</v>
+      </c>
+      <c r="G3030">
+        <v>20.660209</v>
+      </c>
+    </row>
+    <row r="3031">
+      <c r="A3031" t="s">
+        <v>339</v>
+      </c>
+      <c r="B3031" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3031">
+        <v>20</v>
+      </c>
+      <c r="D3031">
+        <v>364600</v>
+      </c>
+      <c r="E3031">
+        <v>3646</v>
+      </c>
+      <c r="F3031">
+        <v>0</v>
+      </c>
+      <c r="G3031">
+        <v>16.278499</v>
+      </c>
+    </row>
+    <row r="3032">
+      <c r="A3032" t="s">
+        <v>339</v>
+      </c>
+      <c r="B3032" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3032">
+        <v>20</v>
+      </c>
+      <c r="D3032">
+        <v>3920400</v>
+      </c>
+      <c r="E3032">
+        <v>39204</v>
+      </c>
+      <c r="F3032">
+        <v>0</v>
+      </c>
+      <c r="G3032">
+        <v>11.64961</v>
+      </c>
+    </row>
+    <row r="3033">
+      <c r="A3033" t="s">
+        <v>339</v>
+      </c>
+      <c r="B3033" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3033">
+        <v>20</v>
+      </c>
+      <c r="D3033">
+        <v>365200</v>
+      </c>
+      <c r="E3033">
+        <v>3652</v>
+      </c>
+      <c r="F3033">
+        <v>0</v>
+      </c>
+      <c r="G3033">
+        <v>18.472999</v>
+      </c>
+    </row>
+    <row r="3034">
+      <c r="A3034" t="s">
+        <v>340</v>
+      </c>
+      <c r="B3034" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3034">
+        <v>20</v>
+      </c>
+      <c r="D3034">
+        <v>351200</v>
+      </c>
+      <c r="E3034">
+        <v>3512</v>
+      </c>
+      <c r="F3034">
+        <v>0</v>
+      </c>
+      <c r="G3034">
+        <v>19.002622</v>
+      </c>
+    </row>
+    <row r="3035">
+      <c r="A3035" t="s">
+        <v>340</v>
+      </c>
+      <c r="B3035" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3035">
+        <v>20</v>
+      </c>
+      <c r="D3035">
+        <v>351200</v>
+      </c>
+      <c r="E3035">
+        <v>3512</v>
+      </c>
+      <c r="F3035">
+        <v>0</v>
+      </c>
+      <c r="G3035">
+        <v>16.368551</v>
+      </c>
+    </row>
+    <row r="3036">
+      <c r="A3036" t="s">
+        <v>340</v>
+      </c>
+      <c r="B3036" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3036">
+        <v>20</v>
+      </c>
+      <c r="D3036">
+        <v>3900300</v>
+      </c>
+      <c r="E3036">
+        <v>39003</v>
+      </c>
+      <c r="F3036">
+        <v>0</v>
+      </c>
+      <c r="G3036">
+        <v>12.414446000000002</v>
+      </c>
+    </row>
+    <row r="3037">
+      <c r="A3037" t="s">
+        <v>340</v>
+      </c>
+      <c r="B3037" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3037">
+        <v>20</v>
+      </c>
+      <c r="D3037">
+        <v>360200</v>
+      </c>
+      <c r="E3037">
+        <v>3602</v>
+      </c>
+      <c r="F3037">
+        <v>0</v>
+      </c>
+      <c r="G3037">
+        <v>18.546211</v>
+      </c>
+    </row>
+    <row r="3038">
+      <c r="A3038" t="s">
+        <v>341</v>
+      </c>
+      <c r="B3038" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3038">
+        <v>20</v>
+      </c>
+      <c r="D3038">
+        <v>347200</v>
+      </c>
+      <c r="E3038">
+        <v>3472</v>
+      </c>
+      <c r="F3038">
+        <v>0</v>
+      </c>
+      <c r="G3038">
+        <v>18.521573999999998</v>
+      </c>
+    </row>
+    <row r="3039">
+      <c r="A3039" t="s">
+        <v>341</v>
+      </c>
+      <c r="B3039" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3039">
+        <v>20</v>
+      </c>
+      <c r="D3039">
+        <v>347200</v>
+      </c>
+      <c r="E3039">
+        <v>3472</v>
+      </c>
+      <c r="F3039">
+        <v>0</v>
+      </c>
+      <c r="G3039">
+        <v>16.503203000000003</v>
+      </c>
+    </row>
+    <row r="3040">
+      <c r="A3040" t="s">
+        <v>341</v>
+      </c>
+      <c r="B3040" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3040">
+        <v>20</v>
+      </c>
+      <c r="D3040">
+        <v>3911000</v>
+      </c>
+      <c r="E3040">
+        <v>39110</v>
+      </c>
+      <c r="F3040">
+        <v>0</v>
+      </c>
+      <c r="G3040">
+        <v>11.756423</v>
+      </c>
+    </row>
+    <row r="3041">
+      <c r="A3041" t="s">
+        <v>341</v>
+      </c>
+      <c r="B3041" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3041">
+        <v>20</v>
+      </c>
+      <c r="D3041">
+        <v>364200</v>
+      </c>
+      <c r="E3041">
+        <v>3642</v>
+      </c>
+      <c r="F3041">
+        <v>0</v>
+      </c>
+      <c r="G3041">
+        <v>17.538194999999998</v>
+      </c>
+    </row>
+    <row r="3042">
+      <c r="A3042" t="s">
+        <v>342</v>
+      </c>
+      <c r="B3042" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3042">
+        <v>20</v>
+      </c>
+      <c r="D3042">
+        <v>353200</v>
+      </c>
+      <c r="E3042">
+        <v>3532</v>
+      </c>
+      <c r="F3042">
+        <v>0</v>
+      </c>
+      <c r="G3042">
+        <v>19.164675</v>
+      </c>
+    </row>
+    <row r="3043">
+      <c r="A3043" t="s">
+        <v>342</v>
+      </c>
+      <c r="B3043" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3043">
+        <v>20</v>
+      </c>
+      <c r="D3043">
+        <v>353200</v>
+      </c>
+      <c r="E3043">
+        <v>3532</v>
+      </c>
+      <c r="F3043">
+        <v>0</v>
+      </c>
+      <c r="G3043">
+        <v>18.767412</v>
+      </c>
+    </row>
+    <row r="3044">
+      <c r="A3044" t="s">
+        <v>342</v>
+      </c>
+      <c r="B3044" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3044">
+        <v>20</v>
+      </c>
+      <c r="D3044">
+        <v>3908200</v>
+      </c>
+      <c r="E3044">
+        <v>39082</v>
+      </c>
+      <c r="F3044">
+        <v>0</v>
+      </c>
+      <c r="G3044">
+        <v>13.449147</v>
+      </c>
+    </row>
+    <row r="3045">
+      <c r="A3045" t="s">
+        <v>342</v>
+      </c>
+      <c r="B3045" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3045">
+        <v>20</v>
+      </c>
+      <c r="D3045">
+        <v>364100</v>
+      </c>
+      <c r="E3045">
+        <v>3641</v>
+      </c>
+      <c r="F3045">
+        <v>0</v>
+      </c>
+      <c r="G3045">
+        <v>20.627108000000003</v>
+      </c>
+    </row>
+    <row r="3046">
+      <c r="A3046" t="s">
+        <v>343</v>
+      </c>
+      <c r="B3046" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3046">
+        <v>20</v>
+      </c>
+      <c r="D3046">
+        <v>352000</v>
+      </c>
+      <c r="E3046">
+        <v>3520</v>
+      </c>
+      <c r="F3046">
+        <v>0</v>
+      </c>
+      <c r="G3046">
+        <v>19.105542</v>
+      </c>
+    </row>
+    <row r="3047">
+      <c r="A3047" t="s">
+        <v>343</v>
+      </c>
+      <c r="B3047" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3047">
+        <v>20</v>
+      </c>
+      <c r="D3047">
+        <v>352000</v>
+      </c>
+      <c r="E3047">
+        <v>3520</v>
+      </c>
+      <c r="F3047">
+        <v>0</v>
+      </c>
+      <c r="G3047">
+        <v>21.602704</v>
+      </c>
+    </row>
+    <row r="3048">
+      <c r="A3048" t="s">
+        <v>343</v>
+      </c>
+      <c r="B3048" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3048">
+        <v>20</v>
+      </c>
+      <c r="D3048">
+        <v>3916200</v>
+      </c>
+      <c r="E3048">
+        <v>39162</v>
+      </c>
+      <c r="F3048">
+        <v>0</v>
+      </c>
+      <c r="G3048">
+        <v>16.018712</v>
+      </c>
+    </row>
+    <row r="3049">
+      <c r="A3049" t="s">
+        <v>343</v>
+      </c>
+      <c r="B3049" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3049">
+        <v>20</v>
+      </c>
+      <c r="D3049">
+        <v>364900</v>
+      </c>
+      <c r="E3049">
+        <v>3649</v>
+      </c>
+      <c r="F3049">
+        <v>0</v>
+      </c>
+      <c r="G3049">
+        <v>19.980225</v>
+      </c>
+    </row>
+    <row r="3050">
+      <c r="A3050" t="s">
+        <v>344</v>
+      </c>
+      <c r="B3050" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3050">
+        <v>20</v>
+      </c>
+      <c r="D3050">
+        <v>357500</v>
+      </c>
+      <c r="E3050">
+        <v>3575</v>
+      </c>
+      <c r="F3050">
+        <v>0</v>
+      </c>
+      <c r="G3050">
+        <v>19.763117</v>
+      </c>
+    </row>
+    <row r="3051">
+      <c r="A3051" t="s">
+        <v>344</v>
+      </c>
+      <c r="B3051" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3051">
+        <v>20</v>
+      </c>
+      <c r="D3051">
+        <v>357500</v>
+      </c>
+      <c r="E3051">
+        <v>3575</v>
+      </c>
+      <c r="F3051">
+        <v>0</v>
+      </c>
+      <c r="G3051">
+        <v>16.348863</v>
+      </c>
+    </row>
+    <row r="3052">
+      <c r="A3052" t="s">
+        <v>344</v>
+      </c>
+      <c r="B3052" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3052">
+        <v>20</v>
+      </c>
+      <c r="D3052">
+        <v>3905500</v>
+      </c>
+      <c r="E3052">
+        <v>39055</v>
+      </c>
+      <c r="F3052">
+        <v>0</v>
+      </c>
+      <c r="G3052">
+        <v>30.455883999999998</v>
+      </c>
+    </row>
+    <row r="3053">
+      <c r="A3053" t="s">
+        <v>344</v>
+      </c>
+      <c r="B3053" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3053">
+        <v>20</v>
+      </c>
+      <c r="D3053">
+        <v>357500</v>
+      </c>
+      <c r="E3053">
+        <v>3575</v>
+      </c>
+      <c r="F3053">
+        <v>0</v>
+      </c>
+      <c r="G3053">
+        <v>18.186025</v>
+      </c>
+    </row>
+    <row r="3054">
+      <c r="A3054" t="s">
+        <v>345</v>
+      </c>
+      <c r="B3054" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3054">
+        <v>20</v>
+      </c>
+      <c r="D3054">
+        <v>364100</v>
+      </c>
+      <c r="E3054">
+        <v>3641</v>
+      </c>
+      <c r="F3054">
+        <v>0</v>
+      </c>
+      <c r="G3054">
+        <v>18.521314</v>
+      </c>
+    </row>
+    <row r="3055">
+      <c r="A3055" t="s">
+        <v>345</v>
+      </c>
+      <c r="B3055" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3055">
+        <v>20</v>
+      </c>
+      <c r="D3055">
+        <v>364100</v>
+      </c>
+      <c r="E3055">
+        <v>3641</v>
+      </c>
+      <c r="F3055">
+        <v>0</v>
+      </c>
+      <c r="G3055">
+        <v>20.638592</v>
+      </c>
+    </row>
+    <row r="3056">
+      <c r="A3056" t="s">
+        <v>345</v>
+      </c>
+      <c r="B3056" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3056">
+        <v>20</v>
+      </c>
+      <c r="D3056">
+        <v>3921700</v>
+      </c>
+      <c r="E3056">
+        <v>39217</v>
+      </c>
+      <c r="F3056">
+        <v>0</v>
+      </c>
+      <c r="G3056">
+        <v>14.262956</v>
+      </c>
+    </row>
+    <row r="3057">
+      <c r="A3057" t="s">
+        <v>345</v>
+      </c>
+      <c r="B3057" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3057">
+        <v>20</v>
+      </c>
+      <c r="D3057">
+        <v>365600</v>
+      </c>
+      <c r="E3057">
+        <v>3656</v>
+      </c>
+      <c r="F3057">
+        <v>0</v>
+      </c>
+      <c r="G3057">
+        <v>22.370455</v>
+      </c>
+    </row>
+    <row r="3058">
+      <c r="A3058" t="s">
+        <v>346</v>
+      </c>
+      <c r="B3058" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3058">
+        <v>20</v>
+      </c>
+      <c r="D3058">
+        <v>357600</v>
+      </c>
+      <c r="E3058">
+        <v>3576</v>
+      </c>
+      <c r="F3058">
+        <v>0</v>
+      </c>
+      <c r="G3058">
+        <v>16.455113</v>
+      </c>
+    </row>
+    <row r="3059">
+      <c r="A3059" t="s">
+        <v>346</v>
+      </c>
+      <c r="B3059" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3059">
+        <v>20</v>
+      </c>
+      <c r="D3059">
+        <v>357600</v>
+      </c>
+      <c r="E3059">
+        <v>3576</v>
+      </c>
+      <c r="F3059">
+        <v>0</v>
+      </c>
+      <c r="G3059">
+        <v>16.979385999999998</v>
+      </c>
+    </row>
+    <row r="3060">
+      <c r="A3060" t="s">
+        <v>346</v>
+      </c>
+      <c r="B3060" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3060">
+        <v>20</v>
+      </c>
+      <c r="D3060">
+        <v>3907300</v>
+      </c>
+      <c r="E3060">
+        <v>39073</v>
+      </c>
+      <c r="F3060">
+        <v>0</v>
+      </c>
+      <c r="G3060">
+        <v>12.762211</v>
+      </c>
+    </row>
+    <row r="3061">
+      <c r="A3061" t="s">
+        <v>346</v>
+      </c>
+      <c r="B3061" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3061">
+        <v>20</v>
+      </c>
+      <c r="D3061">
+        <v>364900</v>
+      </c>
+      <c r="E3061">
+        <v>3649</v>
+      </c>
+      <c r="F3061">
+        <v>0</v>
+      </c>
+      <c r="G3061">
+        <v>18.776186</v>
+      </c>
+    </row>
+    <row r="3062">
+      <c r="A3062" t="s">
+        <v>347</v>
+      </c>
+      <c r="B3062" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3062">
+        <v>20</v>
+      </c>
+      <c r="D3062">
+        <v>352200</v>
+      </c>
+      <c r="E3062">
+        <v>3522</v>
+      </c>
+      <c r="F3062">
+        <v>0</v>
+      </c>
+      <c r="G3062">
+        <v>18.984991</v>
+      </c>
+    </row>
+    <row r="3063">
+      <c r="A3063" t="s">
+        <v>347</v>
+      </c>
+      <c r="B3063" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3063">
+        <v>20</v>
+      </c>
+      <c r="D3063">
+        <v>352200</v>
+      </c>
+      <c r="E3063">
+        <v>3522</v>
+      </c>
+      <c r="F3063">
+        <v>0</v>
+      </c>
+      <c r="G3063">
+        <v>16.747226</v>
+      </c>
+    </row>
+    <row r="3064">
+      <c r="A3064" t="s">
+        <v>347</v>
+      </c>
+      <c r="B3064" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3064">
+        <v>20</v>
+      </c>
+      <c r="D3064">
+        <v>3904000</v>
+      </c>
+      <c r="E3064">
+        <v>39040</v>
+      </c>
+      <c r="F3064">
+        <v>0</v>
+      </c>
+      <c r="G3064">
+        <v>13.975451</v>
+      </c>
+    </row>
+    <row r="3065">
+      <c r="A3065" t="s">
+        <v>347</v>
+      </c>
+      <c r="B3065" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3065">
+        <v>20</v>
+      </c>
+      <c r="D3065">
+        <v>360800</v>
+      </c>
+      <c r="E3065">
+        <v>3608</v>
+      </c>
+      <c r="F3065">
+        <v>0</v>
+      </c>
+      <c r="G3065">
+        <v>19.446187000000002</v>
+      </c>
+    </row>
+    <row r="3066">
+      <c r="A3066" t="s">
+        <v>348</v>
+      </c>
+      <c r="B3066" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3066">
+        <v>20</v>
+      </c>
+      <c r="D3066">
+        <v>346500</v>
+      </c>
+      <c r="E3066">
+        <v>3465</v>
+      </c>
+      <c r="F3066">
+        <v>0</v>
+      </c>
+      <c r="G3066">
+        <v>19.7831</v>
+      </c>
+    </row>
+    <row r="3067">
+      <c r="A3067" t="s">
+        <v>348</v>
+      </c>
+      <c r="B3067" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3067">
+        <v>20</v>
+      </c>
+      <c r="D3067">
+        <v>346500</v>
+      </c>
+      <c r="E3067">
+        <v>3465</v>
+      </c>
+      <c r="F3067">
+        <v>0</v>
+      </c>
+      <c r="G3067">
+        <v>17.32283</v>
+      </c>
+    </row>
+    <row r="3068">
+      <c r="A3068" t="s">
+        <v>348</v>
+      </c>
+      <c r="B3068" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3068">
+        <v>20</v>
+      </c>
+      <c r="D3068">
+        <v>3914700</v>
+      </c>
+      <c r="E3068">
+        <v>39147</v>
+      </c>
+      <c r="F3068">
+        <v>0</v>
+      </c>
+      <c r="G3068">
+        <v>8.386165</v>
+      </c>
+    </row>
+    <row r="3069">
+      <c r="A3069" t="s">
+        <v>348</v>
+      </c>
+      <c r="B3069" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3069">
+        <v>20</v>
+      </c>
+      <c r="D3069">
+        <v>361800</v>
+      </c>
+      <c r="E3069">
+        <v>3618</v>
+      </c>
+      <c r="F3069">
+        <v>0</v>
+      </c>
+      <c r="G3069">
+        <v>17.349309</v>
+      </c>
+    </row>
+    <row r="3070">
+      <c r="A3070" t="s">
+        <v>349</v>
+      </c>
+      <c r="B3070" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3070">
+        <v>20</v>
+      </c>
+      <c r="D3070">
+        <v>357000</v>
+      </c>
+      <c r="E3070">
+        <v>3570</v>
+      </c>
+      <c r="F3070">
+        <v>0</v>
+      </c>
+      <c r="G3070">
+        <v>18.096082</v>
+      </c>
+    </row>
+    <row r="3071">
+      <c r="A3071" t="s">
+        <v>349</v>
+      </c>
+      <c r="B3071" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3071">
+        <v>20</v>
+      </c>
+      <c r="D3071">
+        <v>357000</v>
+      </c>
+      <c r="E3071">
+        <v>3570</v>
+      </c>
+      <c r="F3071">
+        <v>0</v>
+      </c>
+      <c r="G3071">
+        <v>17.482667</v>
+      </c>
+    </row>
+    <row r="3072">
+      <c r="A3072" t="s">
+        <v>349</v>
+      </c>
+      <c r="B3072" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3072">
+        <v>20</v>
+      </c>
+      <c r="D3072">
+        <v>3905100</v>
+      </c>
+      <c r="E3072">
+        <v>39051</v>
+      </c>
+      <c r="F3072">
+        <v>0</v>
+      </c>
+      <c r="G3072">
+        <v>14.557578</v>
+      </c>
+    </row>
+    <row r="3073">
+      <c r="A3073" t="s">
+        <v>349</v>
+      </c>
+      <c r="B3073" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3073">
+        <v>20</v>
+      </c>
+      <c r="D3073">
+        <v>364700</v>
+      </c>
+      <c r="E3073">
+        <v>3647</v>
+      </c>
+      <c r="F3073">
+        <v>0</v>
+      </c>
+      <c r="G3073">
+        <v>20.152979000000002</v>
+      </c>
+    </row>
+    <row r="3074">
+      <c r="A3074" t="s">
+        <v>350</v>
+      </c>
+      <c r="B3074" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3074">
+        <v>20</v>
+      </c>
+      <c r="D3074">
+        <v>359500</v>
+      </c>
+      <c r="E3074">
+        <v>3595</v>
+      </c>
+      <c r="F3074">
+        <v>0</v>
+      </c>
+      <c r="G3074">
+        <v>17.970686999999998</v>
+      </c>
+    </row>
+    <row r="3075">
+      <c r="A3075" t="s">
+        <v>350</v>
+      </c>
+      <c r="B3075" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3075">
+        <v>20</v>
+      </c>
+      <c r="D3075">
+        <v>359500</v>
+      </c>
+      <c r="E3075">
+        <v>3595</v>
+      </c>
+      <c r="F3075">
+        <v>0</v>
+      </c>
+      <c r="G3075">
+        <v>16.137623</v>
+      </c>
+    </row>
+    <row r="3076">
+      <c r="A3076" t="s">
+        <v>350</v>
+      </c>
+      <c r="B3076" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3076">
+        <v>20</v>
+      </c>
+      <c r="D3076">
+        <v>3927700</v>
+      </c>
+      <c r="E3076">
+        <v>39277</v>
+      </c>
+      <c r="F3076">
+        <v>0</v>
+      </c>
+      <c r="G3076">
+        <v>8.947673</v>
+      </c>
+    </row>
+    <row r="3077">
+      <c r="A3077" t="s">
+        <v>350</v>
+      </c>
+      <c r="B3077" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3077">
+        <v>20</v>
+      </c>
+      <c r="D3077">
+        <v>362900</v>
+      </c>
+      <c r="E3077">
+        <v>3629</v>
+      </c>
+      <c r="F3077">
+        <v>0</v>
+      </c>
+      <c r="G3077">
+        <v>18.921765999999998</v>
+      </c>
+    </row>
+    <row r="3078">
+      <c r="A3078" t="s">
+        <v>351</v>
+      </c>
+      <c r="B3078" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3078">
+        <v>20</v>
+      </c>
+      <c r="D3078">
+        <v>369000</v>
+      </c>
+      <c r="E3078">
+        <v>3690</v>
+      </c>
+      <c r="F3078">
+        <v>0</v>
+      </c>
+      <c r="G3078">
+        <v>16.928037</v>
+      </c>
+    </row>
+    <row r="3079">
+      <c r="A3079" t="s">
+        <v>351</v>
+      </c>
+      <c r="B3079" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3079">
+        <v>20</v>
+      </c>
+      <c r="D3079">
+        <v>369000</v>
+      </c>
+      <c r="E3079">
+        <v>3690</v>
+      </c>
+      <c r="F3079">
+        <v>0</v>
+      </c>
+      <c r="G3079">
+        <v>16.701646</v>
+      </c>
+    </row>
+    <row r="3080">
+      <c r="A3080" t="s">
+        <v>351</v>
+      </c>
+      <c r="B3080" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3080">
+        <v>20</v>
+      </c>
+      <c r="D3080">
+        <v>3921100</v>
+      </c>
+      <c r="E3080">
+        <v>39211</v>
+      </c>
+      <c r="F3080">
+        <v>0</v>
+      </c>
+      <c r="G3080">
+        <v>12.46564</v>
+      </c>
+    </row>
+    <row r="3081">
+      <c r="A3081" t="s">
+        <v>351</v>
+      </c>
+      <c r="B3081" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3081">
+        <v>20</v>
+      </c>
+      <c r="D3081">
+        <v>361400</v>
+      </c>
+      <c r="E3081">
+        <v>3614</v>
+      </c>
+      <c r="F3081">
+        <v>0</v>
+      </c>
+      <c r="G3081">
+        <v>18.200656</v>
+      </c>
+    </row>
+    <row r="3082">
+      <c r="A3082" t="s">
+        <v>352</v>
+      </c>
+      <c r="B3082" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3082">
+        <v>20</v>
+      </c>
+      <c r="D3082">
+        <v>362100</v>
+      </c>
+      <c r="E3082">
+        <v>3621</v>
+      </c>
+      <c r="F3082">
+        <v>0</v>
+      </c>
+      <c r="G3082">
+        <v>22.335326</v>
+      </c>
+    </row>
+    <row r="3083">
+      <c r="A3083" t="s">
+        <v>352</v>
+      </c>
+      <c r="B3083" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3083">
+        <v>20</v>
+      </c>
+      <c r="D3083">
+        <v>362100</v>
+      </c>
+      <c r="E3083">
+        <v>3621</v>
+      </c>
+      <c r="F3083">
+        <v>0</v>
+      </c>
+      <c r="G3083">
+        <v>24.831224</v>
+      </c>
+    </row>
+    <row r="3084">
+      <c r="A3084" t="s">
+        <v>352</v>
+      </c>
+      <c r="B3084" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3084">
+        <v>20</v>
+      </c>
+      <c r="D3084">
+        <v>3899900</v>
+      </c>
+      <c r="E3084">
+        <v>38999</v>
+      </c>
+      <c r="F3084">
+        <v>0</v>
+      </c>
+      <c r="G3084">
+        <v>14.442812</v>
+      </c>
+    </row>
+    <row r="3085">
+      <c r="A3085" t="s">
+        <v>352</v>
+      </c>
+      <c r="B3085" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3085">
+        <v>20</v>
+      </c>
+      <c r="D3085">
+        <v>360600</v>
+      </c>
+      <c r="E3085">
+        <v>3606</v>
+      </c>
+      <c r="F3085">
+        <v>0</v>
+      </c>
+      <c r="G3085">
+        <v>21.534779</v>
+      </c>
+    </row>
+    <row r="3086">
+      <c r="A3086" t="s">
+        <v>353</v>
+      </c>
+      <c r="B3086" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3086">
+        <v>20</v>
+      </c>
+      <c r="D3086">
+        <v>364500</v>
+      </c>
+      <c r="E3086">
+        <v>3645</v>
+      </c>
+      <c r="F3086">
+        <v>0</v>
+      </c>
+      <c r="G3086">
+        <v>20.214436</v>
+      </c>
+    </row>
+    <row r="3087">
+      <c r="A3087" t="s">
+        <v>353</v>
+      </c>
+      <c r="B3087" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3087">
+        <v>20</v>
+      </c>
+      <c r="D3087">
+        <v>364500</v>
+      </c>
+      <c r="E3087">
+        <v>3645</v>
+      </c>
+      <c r="F3087">
+        <v>0</v>
+      </c>
+      <c r="G3087">
+        <v>19.604066</v>
+      </c>
+    </row>
+    <row r="3088">
+      <c r="A3088" t="s">
+        <v>353</v>
+      </c>
+      <c r="B3088" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3088">
+        <v>20</v>
+      </c>
+      <c r="D3088">
+        <v>3925600</v>
+      </c>
+      <c r="E3088">
+        <v>39256</v>
+      </c>
+      <c r="F3088">
+        <v>0</v>
+      </c>
+      <c r="G3088">
+        <v>16.444705</v>
+      </c>
+    </row>
+    <row r="3089">
+      <c r="A3089" t="s">
+        <v>353</v>
+      </c>
+      <c r="B3089" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3089">
+        <v>20</v>
+      </c>
+      <c r="D3089">
+        <v>370000</v>
+      </c>
+      <c r="E3089">
+        <v>3700</v>
+      </c>
+      <c r="F3089">
+        <v>0</v>
+      </c>
+      <c r="G3089">
+        <v>19.713745000000003</v>
+      </c>
+    </row>
+    <row r="3090">
+      <c r="A3090" t="s">
+        <v>354</v>
+      </c>
+      <c r="B3090" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3090">
+        <v>20</v>
+      </c>
+      <c r="D3090">
+        <v>345800</v>
+      </c>
+      <c r="E3090">
+        <v>3458</v>
+      </c>
+      <c r="F3090">
+        <v>0</v>
+      </c>
+      <c r="G3090">
+        <v>19.624629000000002</v>
+      </c>
+    </row>
+    <row r="3091">
+      <c r="A3091" t="s">
+        <v>354</v>
+      </c>
+      <c r="B3091" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3091">
+        <v>20</v>
+      </c>
+      <c r="D3091">
+        <v>345800</v>
+      </c>
+      <c r="E3091">
+        <v>3458</v>
+      </c>
+      <c r="F3091">
+        <v>0</v>
+      </c>
+      <c r="G3091">
+        <v>15.701977</v>
+      </c>
+    </row>
+    <row r="3092">
+      <c r="A3092" t="s">
+        <v>354</v>
+      </c>
+      <c r="B3092" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3092">
+        <v>20</v>
+      </c>
+      <c r="D3092">
+        <v>3895400</v>
+      </c>
+      <c r="E3092">
+        <v>38954</v>
+      </c>
+      <c r="F3092">
+        <v>0</v>
+      </c>
+      <c r="G3092">
+        <v>12.122466</v>
+      </c>
+    </row>
+    <row r="3093">
+      <c r="A3093" t="s">
+        <v>354</v>
+      </c>
+      <c r="B3093" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3093">
+        <v>20</v>
+      </c>
+      <c r="D3093">
+        <v>360100</v>
+      </c>
+      <c r="E3093">
+        <v>3601</v>
+      </c>
+      <c r="F3093">
+        <v>0</v>
+      </c>
+      <c r="G3093">
+        <v>18.021999</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/can2tsn_history.xlsx
+++ b/can2tsn_history.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="365">
   <si>
     <t>TimeStamp</t>
   </si>
@@ -1081,6 +1081,36 @@
   <si>
     <t>2025-05-09 17:47:56</t>
   </si>
+  <si>
+    <t>2025-05-09 19:31:25</t>
+  </si>
+  <si>
+    <t>2025-05-09 21:28:42</t>
+  </si>
+  <si>
+    <t>2025-05-09 21:57:48</t>
+  </si>
+  <si>
+    <t>2025-05-09 21:58:11</t>
+  </si>
+  <si>
+    <t>2025-05-09 21:58:36</t>
+  </si>
+  <si>
+    <t>2025-05-09 22:01:51</t>
+  </si>
+  <si>
+    <t>2025-05-09 22:05:44</t>
+  </si>
+  <si>
+    <t>2025-05-09 22:06:02</t>
+  </si>
+  <si>
+    <t>2025-05-09 22:30:37</t>
+  </si>
+  <si>
+    <t>2025-05-09 22:30:47</t>
+  </si>
 </sst>
 </file>
 
@@ -72532,6 +72562,926 @@
         <v>18.021999</v>
       </c>
     </row>
+    <row r="3094">
+      <c r="A3094" t="s">
+        <v>355</v>
+      </c>
+      <c r="B3094" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3094">
+        <v>20</v>
+      </c>
+      <c r="D3094">
+        <v>353400</v>
+      </c>
+      <c r="E3094">
+        <v>3534</v>
+      </c>
+      <c r="F3094">
+        <v>0</v>
+      </c>
+      <c r="G3094">
+        <v>16.507047</v>
+      </c>
+    </row>
+    <row r="3095">
+      <c r="A3095" t="s">
+        <v>355</v>
+      </c>
+      <c r="B3095" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3095">
+        <v>20</v>
+      </c>
+      <c r="D3095">
+        <v>353400</v>
+      </c>
+      <c r="E3095">
+        <v>3534</v>
+      </c>
+      <c r="F3095">
+        <v>0</v>
+      </c>
+      <c r="G3095">
+        <v>18.395376000000002</v>
+      </c>
+    </row>
+    <row r="3096">
+      <c r="A3096" t="s">
+        <v>355</v>
+      </c>
+      <c r="B3096" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3096">
+        <v>20</v>
+      </c>
+      <c r="D3096">
+        <v>3920600</v>
+      </c>
+      <c r="E3096">
+        <v>39206</v>
+      </c>
+      <c r="F3096">
+        <v>0</v>
+      </c>
+      <c r="G3096">
+        <v>17.44868</v>
+      </c>
+    </row>
+    <row r="3097">
+      <c r="A3097" t="s">
+        <v>355</v>
+      </c>
+      <c r="B3097" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3097">
+        <v>20</v>
+      </c>
+      <c r="D3097">
+        <v>365200</v>
+      </c>
+      <c r="E3097">
+        <v>3652</v>
+      </c>
+      <c r="F3097">
+        <v>0</v>
+      </c>
+      <c r="G3097">
+        <v>21.194149999999997</v>
+      </c>
+    </row>
+    <row r="3098">
+      <c r="A3098" t="s">
+        <v>356</v>
+      </c>
+      <c r="B3098" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3098">
+        <v>20</v>
+      </c>
+      <c r="D3098">
+        <v>354400</v>
+      </c>
+      <c r="E3098">
+        <v>3544</v>
+      </c>
+      <c r="F3098">
+        <v>0</v>
+      </c>
+      <c r="G3098">
+        <v>17.146611</v>
+      </c>
+    </row>
+    <row r="3099">
+      <c r="A3099" t="s">
+        <v>356</v>
+      </c>
+      <c r="B3099" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3099">
+        <v>20</v>
+      </c>
+      <c r="D3099">
+        <v>354400</v>
+      </c>
+      <c r="E3099">
+        <v>3544</v>
+      </c>
+      <c r="F3099">
+        <v>0</v>
+      </c>
+      <c r="G3099">
+        <v>24.115119</v>
+      </c>
+    </row>
+    <row r="3100">
+      <c r="A3100" t="s">
+        <v>356</v>
+      </c>
+      <c r="B3100" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3100">
+        <v>20</v>
+      </c>
+      <c r="D3100">
+        <v>3930400</v>
+      </c>
+      <c r="E3100">
+        <v>39304</v>
+      </c>
+      <c r="F3100">
+        <v>0</v>
+      </c>
+      <c r="G3100">
+        <v>14.088747</v>
+      </c>
+    </row>
+    <row r="3101">
+      <c r="A3101" t="s">
+        <v>356</v>
+      </c>
+      <c r="B3101" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3101">
+        <v>20</v>
+      </c>
+      <c r="D3101">
+        <v>359800</v>
+      </c>
+      <c r="E3101">
+        <v>3598</v>
+      </c>
+      <c r="F3101">
+        <v>0</v>
+      </c>
+      <c r="G3101">
+        <v>18.902317</v>
+      </c>
+    </row>
+    <row r="3102">
+      <c r="A3102" t="s">
+        <v>357</v>
+      </c>
+      <c r="B3102" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3102">
+        <v>20</v>
+      </c>
+      <c r="D3102">
+        <v>353700</v>
+      </c>
+      <c r="E3102">
+        <v>3537</v>
+      </c>
+      <c r="F3102">
+        <v>0</v>
+      </c>
+      <c r="G3102">
+        <v>23.762183999999998</v>
+      </c>
+    </row>
+    <row r="3103">
+      <c r="A3103" t="s">
+        <v>357</v>
+      </c>
+      <c r="B3103" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3103">
+        <v>20</v>
+      </c>
+      <c r="D3103">
+        <v>353700</v>
+      </c>
+      <c r="E3103">
+        <v>3537</v>
+      </c>
+      <c r="F3103">
+        <v>0</v>
+      </c>
+      <c r="G3103">
+        <v>17.563892000000003</v>
+      </c>
+    </row>
+    <row r="3104">
+      <c r="A3104" t="s">
+        <v>357</v>
+      </c>
+      <c r="B3104" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3104">
+        <v>20</v>
+      </c>
+      <c r="D3104">
+        <v>3916900</v>
+      </c>
+      <c r="E3104">
+        <v>39169</v>
+      </c>
+      <c r="F3104">
+        <v>0</v>
+      </c>
+      <c r="G3104">
+        <v>10.813758</v>
+      </c>
+    </row>
+    <row r="3105">
+      <c r="A3105" t="s">
+        <v>357</v>
+      </c>
+      <c r="B3105" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3105">
+        <v>20</v>
+      </c>
+      <c r="D3105">
+        <v>358900</v>
+      </c>
+      <c r="E3105">
+        <v>3589</v>
+      </c>
+      <c r="F3105">
+        <v>0</v>
+      </c>
+      <c r="G3105">
+        <v>35.616681</v>
+      </c>
+    </row>
+    <row r="3106">
+      <c r="A3106" t="s">
+        <v>358</v>
+      </c>
+      <c r="B3106" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3106">
+        <v>20</v>
+      </c>
+      <c r="D3106">
+        <v>348300</v>
+      </c>
+      <c r="E3106">
+        <v>3483</v>
+      </c>
+      <c r="F3106">
+        <v>0</v>
+      </c>
+      <c r="G3106">
+        <v>18.80642</v>
+      </c>
+    </row>
+    <row r="3107">
+      <c r="A3107" t="s">
+        <v>358</v>
+      </c>
+      <c r="B3107" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3107">
+        <v>20</v>
+      </c>
+      <c r="D3107">
+        <v>348300</v>
+      </c>
+      <c r="E3107">
+        <v>3483</v>
+      </c>
+      <c r="F3107">
+        <v>0</v>
+      </c>
+      <c r="G3107">
+        <v>20.620824</v>
+      </c>
+    </row>
+    <row r="3108">
+      <c r="A3108" t="s">
+        <v>358</v>
+      </c>
+      <c r="B3108" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3108">
+        <v>20</v>
+      </c>
+      <c r="D3108">
+        <v>3928200</v>
+      </c>
+      <c r="E3108">
+        <v>39282</v>
+      </c>
+      <c r="F3108">
+        <v>0</v>
+      </c>
+      <c r="G3108">
+        <v>12.562267</v>
+      </c>
+    </row>
+    <row r="3109">
+      <c r="A3109" t="s">
+        <v>358</v>
+      </c>
+      <c r="B3109" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3109">
+        <v>20</v>
+      </c>
+      <c r="D3109">
+        <v>366700</v>
+      </c>
+      <c r="E3109">
+        <v>3667</v>
+      </c>
+      <c r="F3109">
+        <v>0</v>
+      </c>
+      <c r="G3109">
+        <v>18.728635</v>
+      </c>
+    </row>
+    <row r="3110">
+      <c r="A3110" t="s">
+        <v>359</v>
+      </c>
+      <c r="B3110" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3110">
+        <v>20</v>
+      </c>
+      <c r="D3110">
+        <v>354300</v>
+      </c>
+      <c r="E3110">
+        <v>3543</v>
+      </c>
+      <c r="F3110">
+        <v>0</v>
+      </c>
+      <c r="G3110">
+        <v>18.956834999999998</v>
+      </c>
+    </row>
+    <row r="3111">
+      <c r="A3111" t="s">
+        <v>359</v>
+      </c>
+      <c r="B3111" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3111">
+        <v>20</v>
+      </c>
+      <c r="D3111">
+        <v>354300</v>
+      </c>
+      <c r="E3111">
+        <v>3543</v>
+      </c>
+      <c r="F3111">
+        <v>0</v>
+      </c>
+      <c r="G3111">
+        <v>16.891986000000003</v>
+      </c>
+    </row>
+    <row r="3112">
+      <c r="A3112" t="s">
+        <v>359</v>
+      </c>
+      <c r="B3112" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3112">
+        <v>20</v>
+      </c>
+      <c r="D3112">
+        <v>3937900</v>
+      </c>
+      <c r="E3112">
+        <v>39379</v>
+      </c>
+      <c r="F3112">
+        <v>0</v>
+      </c>
+      <c r="G3112">
+        <v>8.856203</v>
+      </c>
+    </row>
+    <row r="3113">
+      <c r="A3113" t="s">
+        <v>359</v>
+      </c>
+      <c r="B3113" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3113">
+        <v>20</v>
+      </c>
+      <c r="D3113">
+        <v>370800</v>
+      </c>
+      <c r="E3113">
+        <v>3708</v>
+      </c>
+      <c r="F3113">
+        <v>0</v>
+      </c>
+      <c r="G3113">
+        <v>17.814448</v>
+      </c>
+    </row>
+    <row r="3114">
+      <c r="A3114" t="s">
+        <v>360</v>
+      </c>
+      <c r="B3114" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3114">
+        <v>20</v>
+      </c>
+      <c r="D3114">
+        <v>358200</v>
+      </c>
+      <c r="E3114">
+        <v>3582</v>
+      </c>
+      <c r="F3114">
+        <v>0</v>
+      </c>
+      <c r="G3114">
+        <v>19.755793</v>
+      </c>
+    </row>
+    <row r="3115">
+      <c r="A3115" t="s">
+        <v>360</v>
+      </c>
+      <c r="B3115" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3115">
+        <v>20</v>
+      </c>
+      <c r="D3115">
+        <v>358200</v>
+      </c>
+      <c r="E3115">
+        <v>3582</v>
+      </c>
+      <c r="F3115">
+        <v>0</v>
+      </c>
+      <c r="G3115">
+        <v>17.265372</v>
+      </c>
+    </row>
+    <row r="3116">
+      <c r="A3116" t="s">
+        <v>360</v>
+      </c>
+      <c r="B3116" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3116">
+        <v>20</v>
+      </c>
+      <c r="D3116">
+        <v>3914700</v>
+      </c>
+      <c r="E3116">
+        <v>39147</v>
+      </c>
+      <c r="F3116">
+        <v>0</v>
+      </c>
+      <c r="G3116">
+        <v>8.567889000000001</v>
+      </c>
+    </row>
+    <row r="3117">
+      <c r="A3117" t="s">
+        <v>360</v>
+      </c>
+      <c r="B3117" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3117">
+        <v>20</v>
+      </c>
+      <c r="D3117">
+        <v>365100</v>
+      </c>
+      <c r="E3117">
+        <v>3651</v>
+      </c>
+      <c r="F3117">
+        <v>0</v>
+      </c>
+      <c r="G3117">
+        <v>19.249701</v>
+      </c>
+    </row>
+    <row r="3118">
+      <c r="A3118" t="s">
+        <v>361</v>
+      </c>
+      <c r="B3118" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3118">
+        <v>20</v>
+      </c>
+      <c r="D3118">
+        <v>351900</v>
+      </c>
+      <c r="E3118">
+        <v>3519</v>
+      </c>
+      <c r="F3118">
+        <v>0</v>
+      </c>
+      <c r="G3118">
+        <v>17.325532000000003</v>
+      </c>
+    </row>
+    <row r="3119">
+      <c r="A3119" t="s">
+        <v>361</v>
+      </c>
+      <c r="B3119" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3119">
+        <v>20</v>
+      </c>
+      <c r="D3119">
+        <v>351900</v>
+      </c>
+      <c r="E3119">
+        <v>3519</v>
+      </c>
+      <c r="F3119">
+        <v>0</v>
+      </c>
+      <c r="G3119">
+        <v>17.13896</v>
+      </c>
+    </row>
+    <row r="3120">
+      <c r="A3120" t="s">
+        <v>361</v>
+      </c>
+      <c r="B3120" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3120">
+        <v>20</v>
+      </c>
+      <c r="D3120">
+        <v>3905300</v>
+      </c>
+      <c r="E3120">
+        <v>39053</v>
+      </c>
+      <c r="F3120">
+        <v>0</v>
+      </c>
+      <c r="G3120">
+        <v>12.701828</v>
+      </c>
+    </row>
+    <row r="3121">
+      <c r="A3121" t="s">
+        <v>361</v>
+      </c>
+      <c r="B3121" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3121">
+        <v>20</v>
+      </c>
+      <c r="D3121">
+        <v>361200</v>
+      </c>
+      <c r="E3121">
+        <v>3612</v>
+      </c>
+      <c r="F3121">
+        <v>0</v>
+      </c>
+      <c r="G3121">
+        <v>17.336825</v>
+      </c>
+    </row>
+    <row r="3122">
+      <c r="A3122" t="s">
+        <v>362</v>
+      </c>
+      <c r="B3122" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3122">
+        <v>20</v>
+      </c>
+      <c r="D3122">
+        <v>369500</v>
+      </c>
+      <c r="E3122">
+        <v>3695</v>
+      </c>
+      <c r="F3122">
+        <v>0</v>
+      </c>
+      <c r="G3122">
+        <v>19.152336</v>
+      </c>
+    </row>
+    <row r="3123">
+      <c r="A3123" t="s">
+        <v>362</v>
+      </c>
+      <c r="B3123" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3123">
+        <v>20</v>
+      </c>
+      <c r="D3123">
+        <v>369500</v>
+      </c>
+      <c r="E3123">
+        <v>3695</v>
+      </c>
+      <c r="F3123">
+        <v>0</v>
+      </c>
+      <c r="G3123">
+        <v>16.29487</v>
+      </c>
+    </row>
+    <row r="3124">
+      <c r="A3124" t="s">
+        <v>362</v>
+      </c>
+      <c r="B3124" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3124">
+        <v>20</v>
+      </c>
+      <c r="D3124">
+        <v>3920800</v>
+      </c>
+      <c r="E3124">
+        <v>39208</v>
+      </c>
+      <c r="F3124">
+        <v>0</v>
+      </c>
+      <c r="G3124">
+        <v>12.203722</v>
+      </c>
+    </row>
+    <row r="3125">
+      <c r="A3125" t="s">
+        <v>362</v>
+      </c>
+      <c r="B3125" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3125">
+        <v>20</v>
+      </c>
+      <c r="D3125">
+        <v>366300</v>
+      </c>
+      <c r="E3125">
+        <v>3663</v>
+      </c>
+      <c r="F3125">
+        <v>0</v>
+      </c>
+      <c r="G3125">
+        <v>17.966589000000003</v>
+      </c>
+    </row>
+    <row r="3126">
+      <c r="A3126" t="s">
+        <v>363</v>
+      </c>
+      <c r="B3126" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3126">
+        <v>20</v>
+      </c>
+      <c r="D3126">
+        <v>347200</v>
+      </c>
+      <c r="E3126">
+        <v>3472</v>
+      </c>
+      <c r="F3126">
+        <v>0</v>
+      </c>
+      <c r="G3126">
+        <v>43.593959</v>
+      </c>
+    </row>
+    <row r="3127">
+      <c r="A3127" t="s">
+        <v>363</v>
+      </c>
+      <c r="B3127" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3127">
+        <v>20</v>
+      </c>
+      <c r="D3127">
+        <v>347200</v>
+      </c>
+      <c r="E3127">
+        <v>3472</v>
+      </c>
+      <c r="F3127">
+        <v>0</v>
+      </c>
+      <c r="G3127">
+        <v>18.19565</v>
+      </c>
+    </row>
+    <row r="3128">
+      <c r="A3128" t="s">
+        <v>363</v>
+      </c>
+      <c r="B3128" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3128">
+        <v>20</v>
+      </c>
+      <c r="D3128">
+        <v>3909500</v>
+      </c>
+      <c r="E3128">
+        <v>39095</v>
+      </c>
+      <c r="F3128">
+        <v>0</v>
+      </c>
+      <c r="G3128">
+        <v>9.702113</v>
+      </c>
+    </row>
+    <row r="3129">
+      <c r="A3129" t="s">
+        <v>363</v>
+      </c>
+      <c r="B3129" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3129">
+        <v>20</v>
+      </c>
+      <c r="D3129">
+        <v>364200</v>
+      </c>
+      <c r="E3129">
+        <v>3642</v>
+      </c>
+      <c r="F3129">
+        <v>0</v>
+      </c>
+      <c r="G3129">
+        <v>18.448922</v>
+      </c>
+    </row>
+    <row r="3130">
+      <c r="A3130" t="s">
+        <v>364</v>
+      </c>
+      <c r="B3130" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3130">
+        <v>20</v>
+      </c>
+      <c r="D3130">
+        <v>346700</v>
+      </c>
+      <c r="E3130">
+        <v>3467</v>
+      </c>
+      <c r="F3130">
+        <v>0</v>
+      </c>
+      <c r="G3130">
+        <v>20.338770999999998</v>
+      </c>
+    </row>
+    <row r="3131">
+      <c r="A3131" t="s">
+        <v>364</v>
+      </c>
+      <c r="B3131" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3131">
+        <v>20</v>
+      </c>
+      <c r="D3131">
+        <v>346700</v>
+      </c>
+      <c r="E3131">
+        <v>3467</v>
+      </c>
+      <c r="F3131">
+        <v>0</v>
+      </c>
+      <c r="G3131">
+        <v>19.054628</v>
+      </c>
+    </row>
+    <row r="3132">
+      <c r="A3132" t="s">
+        <v>364</v>
+      </c>
+      <c r="B3132" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3132">
+        <v>20</v>
+      </c>
+      <c r="D3132">
+        <v>3913500</v>
+      </c>
+      <c r="E3132">
+        <v>39135</v>
+      </c>
+      <c r="F3132">
+        <v>0</v>
+      </c>
+      <c r="G3132">
+        <v>10.408542</v>
+      </c>
+    </row>
+    <row r="3133">
+      <c r="A3133" t="s">
+        <v>364</v>
+      </c>
+      <c r="B3133" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3133">
+        <v>20</v>
+      </c>
+      <c r="D3133">
+        <v>375900</v>
+      </c>
+      <c r="E3133">
+        <v>3759</v>
+      </c>
+      <c r="F3133">
+        <v>0</v>
+      </c>
+      <c r="G3133">
+        <v>26.069443</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>